--- a/MLB/postplanner-imports/bb-postplanner-tobi-2026-10-30.xlsx
+++ b/MLB/postplanner-imports/bb-postplanner-tobi-2026-10-30.xlsx
@@ -478,7 +478,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10/30/2026  10:53</t>
+          <t>10/30/2026  10:55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10/30/2026  11:32</t>
+          <t>10/30/2026  11:34</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/30/2026  12:50</t>
+          <t>10/30/2026  12:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -537,7 +537,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/30/2026  13:29</t>
+          <t>10/30/2026  13:31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -558,7 +558,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/30/2026  14:47</t>
+          <t>10/30/2026  14:49</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -578,7 +578,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/30/2026  15:26</t>
+          <t>10/30/2026  15:28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/30/2026  16:05</t>
+          <t>10/30/2026  16:07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -618,7 +618,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/30/2026  17:23</t>
+          <t>10/30/2026  17:25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/30/2026  18:02</t>
+          <t>10/30/2026  18:04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,7 +656,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/30/2026  18:41</t>
+          <t>10/30/2026  18:43</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/30/2026  19:59</t>
+          <t>10/30/2026  20:01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -696,7 +696,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/30/2026  20:38</t>
+          <t>10/30/2026  20:40</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
